--- a/static/excel/NKE_model.xlsx
+++ b/static/excel/NKE_model.xlsx
@@ -7344,11 +7344,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>65625.088667</v>
+        <v>65499.426749</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $44.39</t>
+          <t>FMP marketCap  |  price $44.305</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-20</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7644,25 +7644,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0507</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A3CAEY — A</t>
         </is>
       </c>
     </row>
@@ -7748,11 +7750,11 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0427</v>
+        <v>0.0454</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -7813,16 +7815,16 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B45" s="55">
-        <f>B8*B28+B9*B38*(1-B42)</f>
+        <f>MAX(0.085, B8*B28+B9*B38*(1-B42))</f>
         <v/>
       </c>
       <c r="C45" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9453,7 @@
         </is>
       </c>
       <c r="B38" s="100" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C38" s="98" t="n"/>
       <c r="D38" s="98" t="n"/>
@@ -9465,7 +9467,7 @@
       <c r="L38" s="98" t="n"/>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>Growth tier: LOW (0.0% 3yr avg rev growth).  Bear 8x / Base 10x / Bull 12x.  Override manually if needed.</t>
+          <t>Growth tier: LOW (0.0% 3yr avg rev growth).  Bear 15x / Base 19x / Bull 23x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9969,7 @@
         </is>
       </c>
       <c r="B61" s="111" t="n">
-        <v>44.39</v>
+        <v>44.3</v>
       </c>
       <c r="C61" s="103" t="n"/>
       <c r="D61" s="103" t="n"/>
@@ -10067,7 +10069,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — NKE  |  Master Prompt v2  |  22 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — NKE  |  Master Prompt v2  |  26 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10586,7 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Current 27.9x  |  5yr avg 30.7x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.37 | no_fwd_data(fallback) | abs=4.0 → blended 40/40/20=7.49]</t>
+          <t>Fwd P/E 29.7x (scoring basis)  |  5yr avg 30.7x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.49 | fwd_pe=29.7x→7.49 | abs=4.0 → blended 40/40/20=6.79]  [revision:Earnings headwind→-0.50]</t>
         </is>
       </c>
       <c r="E22" s="130" t="inlineStr">
@@ -10593,7 +10595,7 @@
         </is>
       </c>
       <c r="F22" s="131" t="n">
-        <v>7.49</v>
+        <v>6.29</v>
       </c>
       <c r="G22" s="132">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10601,7 +10603,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Current 27.9x  |  5yr avg 30.7x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.37 | no_fwd_data(fallback) | abs=4.0 → blended 40/40/20=7.49]</t>
+          <t>Fwd P/E 29.7x (scoring basis)  |  5yr avg 30.7x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.49 | fwd_pe=29.7x→7.49 | abs=4.0 → blended 40/40/20=6.79]  [revision:Earnings headwind→-0.50]</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10623,7 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 27.5x  |  5yr avg 32.1x  |  DCF-implied 19.1x [ref only — not used as benchmark]  [-14% vs benchmark]  [trail=9.15 | no_fwd_data(fallback) | abs=7.5 → blended 40/40/20=8.82]  [fcf_yield=3.6% vs rf=4.6%  spread=-0.9%→modifier=-0.25]</t>
+          <t>Current 27.5x  |  5yr avg 32.1x  |  DCF-implied 19.1x [ref only — not used as benchmark]  [-14% vs benchmark]  [trail=9.15 | fwd_pfcf=20.2x→10.00 | abs=7.5 → blended 40/40/20=9.16]  [fcf_yield=3.6% vs rf=4.6%  spread=-0.9%→modifier=-0.25]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10630,7 +10632,7 @@
         </is>
       </c>
       <c r="F23" s="131" t="n">
-        <v>8.57</v>
+        <v>8.91</v>
       </c>
       <c r="G23" s="132">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10638,7 +10640,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 27.5x  |  5yr avg 32.1x  |  DCF-implied 19.1x [ref only — not used as benchmark]  [-14% vs benchmark]  [trail=9.15 | no_fwd_data(fallback) | abs=7.5 → blended 40/40/20=8.82]  [fcf_yield=3.6% vs rf=4.6%  spread=-0.9%→modifier=-0.25]</t>
+          <t>Current 27.5x  |  5yr avg 32.1x  |  DCF-implied 19.1x [ref only — not used as benchmark]  [-14% vs benchmark]  [trail=9.15 | fwd_pfcf=20.2x→10.00 | abs=7.5 → blended 40/40/20=9.16]  [fcf_yield=3.6% vs rf=4.6%  spread=-0.9%→modifier=-0.25]</t>
         </is>
       </c>
     </row>

--- a/static/excel/NKE_model.xlsx
+++ b/static/excel/NKE_model.xlsx
@@ -7344,11 +7344,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>65499.426749</v>
+        <v>70030.64767200001</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $44.305</t>
+          <t>FMP marketCap  |  price $47.37</t>
         </is>
       </c>
     </row>
@@ -7430,11 +7430,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.043</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: None</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.043</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7513,11 +7513,11 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Damodaran re-levered  (D/E = 0.12x,  t = 17.1%)</t>
+          <t>Damodaran re-levered  (D/E = 0.11x,  t = 17.1%)</t>
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.101</v>
+        <v>1.094</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="B20" s="51" t="n">
-        <v>1.103</v>
+        <v>1.1</v>
       </c>
       <c r="C20" s="49" t="inlineStr">
         <is>
@@ -7656,15 +7656,13 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield  (rating-tier index)</t>
-        </is>
-      </c>
-      <c r="B32" s="46" t="n">
-        <v>0.0507</v>
-      </c>
+          <t>FRED matched yield</t>
+        </is>
+      </c>
+      <c r="B32" s="53" t="n"/>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>FRED BAMLC0A3CAEY — A</t>
+          <t>No rating returned — FRED method not applicable</t>
         </is>
       </c>
     </row>
@@ -7707,11 +7705,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.0484</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.54%</t>
+          <t>Rf 4.30% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7750,11 +7748,11 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.0454</v>
+        <v>0.0413</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 3 source(s) above — override freely</t>
+          <t>Default = average of 2 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9967,7 @@
         </is>
       </c>
       <c r="B61" s="111" t="n">
-        <v>44.3</v>
+        <v>47.37</v>
       </c>
       <c r="C61" s="103" t="n"/>
       <c r="D61" s="103" t="n"/>
@@ -10069,7 +10067,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — NKE  |  Master Prompt v2  |  26 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — NKE  |  Master Prompt v2  |  29 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10200,7 @@
       </c>
       <c r="D9" s="129" t="inlineStr">
         <is>
-          <t>GM 42.7% ✓ (&gt;40%)  |  GM trend -3.2% ✗ (&gt;+1pp)  |  ROIC-WACC +13.8% ✓ (&gt;+5pp)  |  Rev consistency σ=7.2% ✓ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
+          <t>GM 42.7% ✓ (&gt;40%)  |  GM trend -3.2% ✗ (&gt;+1pp)  |  ROIC-WACC +13.7% ✓ (&gt;+5pp)  |  Rev consistency σ=7.2% ✓ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="130" t="inlineStr">
@@ -10219,7 +10217,7 @@
       </c>
       <c r="H9" s="133" t="inlineStr">
         <is>
-          <t>GM 42.7% ✓ (&gt;40%)  |  GM trend -3.2% ✗ (&gt;+1pp)  |  ROIC-WACC +13.8% ✓ (&gt;+5pp)  |  Rev consistency σ=7.2% ✓ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
+          <t>GM 42.7% ✓ (&gt;40%)  |  GM trend -3.2% ✗ (&gt;+1pp)  |  ROIC-WACC +13.7% ✓ (&gt;+5pp)  |  Rev consistency σ=7.2% ✓ (&lt;8%)  [3/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10584,7 @@
       </c>
       <c r="D22" s="129" t="inlineStr">
         <is>
-          <t>Fwd P/E 29.7x (scoring basis)  |  5yr avg 30.7x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.49 | fwd_pe=29.7x→7.49 | abs=4.0 → blended 40/40/20=6.79]  [revision:Earnings headwind→-0.50]</t>
+          <t>Fwd P/E 31.7x (scoring basis)  |  5yr avg 30.7x  |  DCF-implied 20.1x [ref only — not used as benchmark]  [+3% vs benchmark]  [trail=6.48 | fwd_pe=31.7x→6.48 | abs=4.0 → blended 40/40/20=5.98]  [revision:Earnings headwind→-0.50]</t>
         </is>
       </c>
       <c r="E22" s="130" t="inlineStr">
@@ -10595,7 +10593,7 @@
         </is>
       </c>
       <c r="F22" s="131" t="n">
-        <v>6.29</v>
+        <v>5.48</v>
       </c>
       <c r="G22" s="132">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10603,7 +10601,7 @@
       </c>
       <c r="H22" s="133" t="inlineStr">
         <is>
-          <t>Fwd P/E 29.7x (scoring basis)  |  5yr avg 30.7x  |  DCF-implied 19.4x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.49 | fwd_pe=29.7x→7.49 | abs=4.0 → blended 40/40/20=6.79]  [revision:Earnings headwind→-0.50]</t>
+          <t>Fwd P/E 31.7x (scoring basis)  |  5yr avg 30.7x  |  DCF-implied 20.1x [ref only — not used as benchmark]  [+3% vs benchmark]  [trail=6.48 | fwd_pe=31.7x→6.48 | abs=4.0 → blended 40/40/20=5.98]  [revision:Earnings headwind→-0.50]</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10621,7 @@
       </c>
       <c r="D23" s="129" t="inlineStr">
         <is>
-          <t>Current 27.5x  |  5yr avg 32.1x  |  DCF-implied 19.1x [ref only — not used as benchmark]  [-14% vs benchmark]  [trail=9.15 | fwd_pfcf=20.2x→10.00 | abs=7.5 → blended 40/40/20=9.16]  [fcf_yield=3.6% vs rf=4.6%  spread=-0.9%→modifier=-0.25]</t>
+          <t>Current 27.5x  |  5yr avg 32.1x  |  DCF-implied 19.8x [ref only — not used as benchmark]  [-14% vs benchmark]  [trail=9.15 | fwd_pfcf=21.5x→10.00 | abs=7.5 → blended 40/40/20=9.16]  [fcf_yield=3.6% vs rf=4.3%  spread=-0.7%→modifier=-0.25]</t>
         </is>
       </c>
       <c r="E23" s="136" t="inlineStr">
@@ -10640,7 +10638,7 @@
       </c>
       <c r="H23" s="133" t="inlineStr">
         <is>
-          <t>Current 27.5x  |  5yr avg 32.1x  |  DCF-implied 19.1x [ref only — not used as benchmark]  [-14% vs benchmark]  [trail=9.15 | fwd_pfcf=20.2x→10.00 | abs=7.5 → blended 40/40/20=9.16]  [fcf_yield=3.6% vs rf=4.6%  spread=-0.9%→modifier=-0.25]</t>
+          <t>Current 27.5x  |  5yr avg 32.1x  |  DCF-implied 19.8x [ref only — not used as benchmark]  [-14% vs benchmark]  [trail=9.15 | fwd_pfcf=21.5x→10.00 | abs=7.5 → blended 40/40/20=9.16]  [fcf_yield=3.6% vs rf=4.3%  spread=-0.7%→modifier=-0.25]</t>
         </is>
       </c>
     </row>
